--- a/data/nzd0195/nzd0195.xlsx
+++ b/data/nzd0195/nzd0195.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H686"/>
+  <dimension ref="A1:H692"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21018,6 +21018,186 @@
         <v>354.3</v>
       </c>
       <c r="H686" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-27 21:59:12+00:00</t>
+        </is>
+      </c>
+      <c r="B687" t="n">
+        <v>332.78</v>
+      </c>
+      <c r="C687" t="n">
+        <v>343.71</v>
+      </c>
+      <c r="D687" t="n">
+        <v>355.92</v>
+      </c>
+      <c r="E687" t="n">
+        <v>364.23</v>
+      </c>
+      <c r="F687" t="n">
+        <v>360.94</v>
+      </c>
+      <c r="G687" t="n">
+        <v>353.72</v>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B688" t="n">
+        <v>332.47</v>
+      </c>
+      <c r="C688" t="n">
+        <v>343.94</v>
+      </c>
+      <c r="D688" t="n">
+        <v>354.02</v>
+      </c>
+      <c r="E688" t="n">
+        <v>363.28</v>
+      </c>
+      <c r="F688" t="n">
+        <v>360.02</v>
+      </c>
+      <c r="G688" t="n">
+        <v>353.14</v>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B689" t="n">
+        <v>333.48</v>
+      </c>
+      <c r="C689" t="n">
+        <v>343.84</v>
+      </c>
+      <c r="D689" t="n">
+        <v>352.78</v>
+      </c>
+      <c r="E689" t="n">
+        <v>361.75</v>
+      </c>
+      <c r="F689" t="n">
+        <v>359.4</v>
+      </c>
+      <c r="G689" t="n">
+        <v>352.88</v>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:59:16+00:00</t>
+        </is>
+      </c>
+      <c r="B690" t="n">
+        <v>334.07</v>
+      </c>
+      <c r="C690" t="n">
+        <v>344.38</v>
+      </c>
+      <c r="D690" t="n">
+        <v>353.47</v>
+      </c>
+      <c r="E690" t="n">
+        <v>362.29</v>
+      </c>
+      <c r="F690" t="n">
+        <v>359.45</v>
+      </c>
+      <c r="G690" t="n">
+        <v>353.36</v>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B691" t="n">
+        <v>334.88</v>
+      </c>
+      <c r="C691" t="n">
+        <v>344.42</v>
+      </c>
+      <c r="D691" t="n">
+        <v>354.16</v>
+      </c>
+      <c r="E691" t="n">
+        <v>363.09</v>
+      </c>
+      <c r="F691" t="n">
+        <v>359.62</v>
+      </c>
+      <c r="G691" t="n">
+        <v>353.16</v>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B692" t="n">
+        <v>336.04</v>
+      </c>
+      <c r="C692" t="n">
+        <v>344.8</v>
+      </c>
+      <c r="D692" t="n">
+        <v>354.86</v>
+      </c>
+      <c r="E692" t="n">
+        <v>363.37</v>
+      </c>
+      <c r="F692" t="n">
+        <v>359.65</v>
+      </c>
+      <c r="G692" t="n">
+        <v>352.99</v>
+      </c>
+      <c r="H692" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -21034,7 +21214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B731"/>
+  <dimension ref="A1:B737"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28347,6 +28527,66 @@
       </c>
       <c r="B731" t="n">
         <v>-0.66</v>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>2026-06-27 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B732" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B733" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B734" t="n">
+        <v>-0.85</v>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>2026-07-13 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B735" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B736" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B737" t="n">
+        <v>-0.33</v>
       </c>
     </row>
   </sheetData>
@@ -28515,28 +28755,28 @@
         <v>0.1248</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2697643700116975</v>
+        <v>0.2505567290546787</v>
       </c>
       <c r="J2" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="K2" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04622474030434343</v>
+        <v>0.04033698387833062</v>
       </c>
       <c r="M2" t="n">
-        <v>7.533339365202852</v>
+        <v>7.554864683420004</v>
       </c>
       <c r="N2" t="n">
-        <v>82.59834648647504</v>
+        <v>82.98178178800521</v>
       </c>
       <c r="O2" t="n">
-        <v>9.088363245737652</v>
+        <v>9.109433669993168</v>
       </c>
       <c r="P2" t="n">
-        <v>338.0181510248367</v>
+        <v>338.2298483366719</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28593,28 +28833,28 @@
         <v>0.1053</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1646228858240193</v>
+        <v>0.1492329164457881</v>
       </c>
       <c r="J3" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="K3" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02056660692853574</v>
+        <v>0.01711036502297258</v>
       </c>
       <c r="M3" t="n">
-        <v>6.964869936166672</v>
+        <v>6.962327552625506</v>
       </c>
       <c r="N3" t="n">
-        <v>70.99426771769492</v>
+        <v>71.07715091960837</v>
       </c>
       <c r="O3" t="n">
-        <v>8.425809617935533</v>
+        <v>8.430726594998108</v>
       </c>
       <c r="P3" t="n">
-        <v>348.8285135553914</v>
+        <v>348.9981472101295</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28671,28 +28911,28 @@
         <v>0.1495</v>
       </c>
       <c r="I4" t="n">
-        <v>0.02601525861940461</v>
+        <v>0.0133584814163292</v>
       </c>
       <c r="J4" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="K4" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0005862504381914935</v>
+        <v>0.0001563633911169093</v>
       </c>
       <c r="M4" t="n">
-        <v>6.551606027939018</v>
+        <v>6.554846045447328</v>
       </c>
       <c r="N4" t="n">
-        <v>63.46715613215081</v>
+        <v>63.39667271662768</v>
       </c>
       <c r="O4" t="n">
-        <v>7.966627651155212</v>
+        <v>7.962202755307584</v>
       </c>
       <c r="P4" t="n">
-        <v>360.97142183285</v>
+        <v>361.1109410113052</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28749,28 +28989,28 @@
         <v>0.1437</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.07600098976106952</v>
+        <v>-0.0809009034276984</v>
       </c>
       <c r="J5" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="K5" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006652249815337186</v>
+        <v>0.007659587477899299</v>
       </c>
       <c r="M5" t="n">
-        <v>5.635161925756045</v>
+        <v>5.613733175595992</v>
       </c>
       <c r="N5" t="n">
-        <v>47.44624667236491</v>
+        <v>47.11045709875912</v>
       </c>
       <c r="O5" t="n">
-        <v>6.888123595897863</v>
+        <v>6.863705784687971</v>
       </c>
       <c r="P5" t="n">
-        <v>367.9447388702984</v>
+        <v>367.9987552102113</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28827,28 +29067,28 @@
         <v>0.1645</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.00937924881567738</v>
+        <v>-0.01180217733034034</v>
       </c>
       <c r="J6" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="K6" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="L6" t="n">
-        <v>9.319043677891159e-05</v>
+        <v>0.0001502729229407862</v>
       </c>
       <c r="M6" t="n">
-        <v>5.801858129153025</v>
+        <v>5.765425958733742</v>
       </c>
       <c r="N6" t="n">
-        <v>51.9224165232532</v>
+        <v>51.49126335295997</v>
       </c>
       <c r="O6" t="n">
-        <v>7.205721096687909</v>
+        <v>7.175741310342784</v>
       </c>
       <c r="P6" t="n">
-        <v>361.5288357436962</v>
+        <v>361.5555517721289</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28905,28 +29145,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06770972207944918</v>
+        <v>0.07112055699126794</v>
       </c>
       <c r="J7" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="K7" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004905045754210358</v>
+        <v>0.005506575805432568</v>
       </c>
       <c r="M7" t="n">
-        <v>5.71179387605809</v>
+        <v>5.678383589720725</v>
       </c>
       <c r="N7" t="n">
-        <v>51.16277917814116</v>
+        <v>50.75348511963663</v>
       </c>
       <c r="O7" t="n">
-        <v>7.152816171141347</v>
+        <v>7.124148027633664</v>
       </c>
       <c r="P7" t="n">
-        <v>349.3671203732634</v>
+        <v>349.3295273166725</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28964,7 +29204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H686"/>
+  <dimension ref="A1:H692"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57779,6 +58019,258 @@
         </is>
       </c>
     </row>
+    <row r="687">
+      <c r="A687" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-27 21:59:12+00:00</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>-37.181074990479004,175.88499301873185</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>-37.1817707770958,175.88522745241113</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>-37.1824668266281,175.8854759849043</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>-37.18313626840201,175.8857829700818</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>-37.1838139086806,175.8860650974914</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>-37.1844972137897,175.88634848556532</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>-37.18107539518716,175.88498956602223</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>-37.181770476823445,175.88523001412116</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>-37.18247032222144,175.88545504783727</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>-37.18313899400242,175.88577283304411</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>-37.183817175351756,175.88605557973688</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>-37.18449938574941,175.88634254749616</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>-37.1810740766215,175.8850008151727</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>-37.181770607376656,175.8852289003342</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>-37.18247260355409,175.88544138364495</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>-37.183143383651846,175.8857565070765</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>-37.183819376803655,175.88604916559746</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>-37.18450035938643,175.88633988560295</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-13 21:59:16+00:00</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>-37.181073306369804,175.88500738645843</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>-37.18176990238924,175.88523491478375</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>-37.182471334103056,175.8854489871069</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>-37.18314183436405,175.88576226918295</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>-37.18381919926723,175.8860496828668</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>-37.18449856190265,175.88634479986723</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-20 22:05:32+00:00</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>-37.181072248905025,175.8850164080538</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>-37.18176985016794,175.8852353602985</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>-37.18247006465154,175.8854565905686</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>-37.18313953912241,175.88577080563647</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>-37.18381859564333,175.88605144158248</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>-37.18449931085425,175.88634275225715</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:48+00:00</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>-37.18107073450982,175.88502932786886</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>-37.18176935406549,175.88523959268886</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>-37.182468776801684,175.88546430422508</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>-37.183138735787686,175.8857737933951</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>-37.183818489121464,175.88605175194405</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>-37.184499947463074,175.88634101178855</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0195/nzd0195.xlsx
+++ b/data/nzd0195/nzd0195.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H692"/>
+  <dimension ref="A1:H695"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21198,6 +21198,96 @@
         <v>352.99</v>
       </c>
       <c r="H692" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B693" t="n">
+        <v>337.78</v>
+      </c>
+      <c r="C693" t="n">
+        <v>345.91</v>
+      </c>
+      <c r="D693" t="n">
+        <v>355.88</v>
+      </c>
+      <c r="E693" t="n">
+        <v>364.39</v>
+      </c>
+      <c r="F693" t="n">
+        <v>360.08</v>
+      </c>
+      <c r="G693" t="n">
+        <v>353.34</v>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-06 21:59:39+00:00</t>
+        </is>
+      </c>
+      <c r="B694" t="n">
+        <v>339.27</v>
+      </c>
+      <c r="C694" t="n">
+        <v>347.48</v>
+      </c>
+      <c r="D694" t="n">
+        <v>356.91</v>
+      </c>
+      <c r="E694" t="n">
+        <v>365.14</v>
+      </c>
+      <c r="F694" t="n">
+        <v>360.8</v>
+      </c>
+      <c r="G694" t="n">
+        <v>353.57</v>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-22 21:59:40+00:00</t>
+        </is>
+      </c>
+      <c r="B695" t="n">
+        <v>339.27</v>
+      </c>
+      <c r="C695" t="n">
+        <v>350.11</v>
+      </c>
+      <c r="D695" t="n">
+        <v>356.91</v>
+      </c>
+      <c r="E695" t="n">
+        <v>365.14</v>
+      </c>
+      <c r="F695" t="n">
+        <v>360.83</v>
+      </c>
+      <c r="G695" t="n">
+        <v>353.16</v>
+      </c>
+      <c r="H695" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -21214,7 +21304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B737"/>
+  <dimension ref="A1:B740"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28587,6 +28677,36 @@
       </c>
       <c r="B737" t="n">
         <v>-0.33</v>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B738" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>2026-08-06 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B739" t="n">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>2026-08-22 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B740" t="n">
+        <v>-0.45</v>
       </c>
     </row>
   </sheetData>
@@ -28755,28 +28875,28 @@
         <v>0.1248</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2505567290546787</v>
+        <v>0.2453075832816598</v>
       </c>
       <c r="J2" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="K2" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="L2" t="n">
-        <v>0.04033698387833062</v>
+        <v>0.03899809265448517</v>
       </c>
       <c r="M2" t="n">
-        <v>7.554864683420004</v>
+        <v>7.546842772873796</v>
       </c>
       <c r="N2" t="n">
-        <v>82.98178178800521</v>
+        <v>82.79119234497695</v>
       </c>
       <c r="O2" t="n">
-        <v>9.109433669993168</v>
+        <v>9.098966553679432</v>
       </c>
       <c r="P2" t="n">
-        <v>338.2298483366719</v>
+        <v>338.2879059546619</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28833,28 +28953,28 @@
         <v>0.1053</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1492329164457881</v>
+        <v>0.1448546756269568</v>
       </c>
       <c r="J3" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="K3" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01711036502297258</v>
+        <v>0.01625519581980761</v>
       </c>
       <c r="M3" t="n">
-        <v>6.962327552625506</v>
+        <v>6.94851329038003</v>
       </c>
       <c r="N3" t="n">
-        <v>71.07715091960837</v>
+        <v>70.89842515044221</v>
       </c>
       <c r="O3" t="n">
-        <v>8.430726594998108</v>
+        <v>8.420120257481019</v>
       </c>
       <c r="P3" t="n">
-        <v>348.9981472101295</v>
+        <v>349.0465610678963</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28911,28 +29031,28 @@
         <v>0.1495</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0133584814163292</v>
+        <v>0.009233014839166271</v>
       </c>
       <c r="J4" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="K4" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0001563633911169093</v>
+        <v>7.527292269338126e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>6.554846045447328</v>
+        <v>6.546152355289504</v>
       </c>
       <c r="N4" t="n">
-        <v>63.39667271662768</v>
+        <v>63.22617407747765</v>
       </c>
       <c r="O4" t="n">
-        <v>7.962202755307584</v>
+        <v>7.951488796286998</v>
       </c>
       <c r="P4" t="n">
-        <v>361.1109410113052</v>
+        <v>361.1565705735921</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28989,28 +29109,28 @@
         <v>0.1437</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0809009034276984</v>
+        <v>-0.08167508019609913</v>
       </c>
       <c r="J5" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="K5" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007659587477899299</v>
+        <v>0.007876835165738783</v>
       </c>
       <c r="M5" t="n">
-        <v>5.613733175595992</v>
+        <v>5.593767428069027</v>
       </c>
       <c r="N5" t="n">
-        <v>47.11045709875912</v>
+        <v>46.91095544522312</v>
       </c>
       <c r="O5" t="n">
-        <v>6.863705784687971</v>
+        <v>6.849157279930365</v>
       </c>
       <c r="P5" t="n">
-        <v>367.9987552102113</v>
+        <v>368.0073167511848</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29067,28 +29187,28 @@
         <v>0.1645</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.01180217733034034</v>
+        <v>-0.01236430322361549</v>
       </c>
       <c r="J6" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="K6" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001502729229407862</v>
+        <v>0.0001664468723451273</v>
       </c>
       <c r="M6" t="n">
-        <v>5.765425958733742</v>
+        <v>5.743713572422441</v>
       </c>
       <c r="N6" t="n">
-        <v>51.49126335295997</v>
+        <v>51.27110401562619</v>
       </c>
       <c r="O6" t="n">
-        <v>7.175741310342784</v>
+        <v>7.160384348317218</v>
       </c>
       <c r="P6" t="n">
-        <v>361.5555517721289</v>
+        <v>361.5617677494131</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29145,28 +29265,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07112055699126794</v>
+        <v>0.07288814994514488</v>
       </c>
       <c r="J7" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="K7" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005506575805432568</v>
+        <v>0.005833204106648449</v>
       </c>
       <c r="M7" t="n">
-        <v>5.678383589720725</v>
+        <v>5.662227854386514</v>
       </c>
       <c r="N7" t="n">
-        <v>50.75348511963663</v>
+        <v>50.55303592057208</v>
       </c>
       <c r="O7" t="n">
-        <v>7.124148027633664</v>
+        <v>7.11006581689453</v>
       </c>
       <c r="P7" t="n">
-        <v>349.3295273166725</v>
+        <v>349.3099771111349</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29204,7 +29324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H692"/>
+  <dimension ref="A1:H695"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58271,6 +58391,132 @@
         </is>
       </c>
     </row>
+    <row r="693">
+      <c r="A693" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:40+00:00</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>-37.1810684629144,175.88504870759036</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>-37.18176790492326,175.8852519557234</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>-37.18246690021959,175.88547554412398</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>-37.183135809353445,175.8857846773723</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>-37.183816962308,175.88605620046005</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>-37.184498636797805,175.88634459510624</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-06 21:59:39+00:00</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>-37.18106651769518,175.885065302868</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>-37.181765855233444,175.8852694421767</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>-37.182465005238555,175.8854868942173</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>-37.183133657562955,175.88579268029613</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>-37.18381440578278,175.88606364913753</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>-37.184497775503424,175.8863469498578</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-22 21:59:40+00:00</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>-37.18106651769518,175.885065302868</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>-37.18176242167092,175.88529873476799</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>-37.182465005238555,175.8854868942173</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>-37.183133657562955,175.88579268029613</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>-37.18381429926089,175.88606395949907</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>-37.18449931085425,175.88634275225715</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0195/nzd0195.xlsx
+++ b/data/nzd0195/nzd0195.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H695"/>
+  <dimension ref="A1:H697"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21288,6 +21288,66 @@
         <v>353.16</v>
       </c>
       <c r="H695" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-07 21:59:48+00:00</t>
+        </is>
+      </c>
+      <c r="B696" t="n">
+        <v>339.47</v>
+      </c>
+      <c r="C696" t="n">
+        <v>350.07</v>
+      </c>
+      <c r="D696" t="n">
+        <v>356.89</v>
+      </c>
+      <c r="E696" t="n">
+        <v>364.95</v>
+      </c>
+      <c r="F696" t="n">
+        <v>361.14</v>
+      </c>
+      <c r="G696" t="n">
+        <v>353.5</v>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-23 21:59:53+00:00</t>
+        </is>
+      </c>
+      <c r="B697" t="n">
+        <v>339.6</v>
+      </c>
+      <c r="C697" t="n">
+        <v>350.28</v>
+      </c>
+      <c r="D697" t="n">
+        <v>356.85</v>
+      </c>
+      <c r="E697" t="n">
+        <v>365</v>
+      </c>
+      <c r="F697" t="n">
+        <v>361.13</v>
+      </c>
+      <c r="G697" t="n">
+        <v>354.15</v>
+      </c>
+      <c r="H697" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -21304,7 +21364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B740"/>
+  <dimension ref="A1:B743"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28707,6 +28767,36 @@
       </c>
       <c r="B740" t="n">
         <v>-0.45</v>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>2026-08-30 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B741" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>2026-09-07 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B742" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>2026-09-23 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B743" t="n">
+        <v>-0.55</v>
       </c>
     </row>
   </sheetData>
@@ -28875,28 +28965,28 @@
         <v>0.1248</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2453075832816598</v>
+        <v>0.2422693002947882</v>
       </c>
       <c r="J2" t="n">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="K2" t="n">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03899809265448517</v>
+        <v>0.03826388504461231</v>
       </c>
       <c r="M2" t="n">
-        <v>7.546842772873796</v>
+        <v>7.539308196719717</v>
       </c>
       <c r="N2" t="n">
-        <v>82.79119234497695</v>
+        <v>82.63687705762436</v>
       </c>
       <c r="O2" t="n">
-        <v>9.098966553679432</v>
+        <v>9.090482773627832</v>
       </c>
       <c r="P2" t="n">
-        <v>338.2879059546619</v>
+        <v>338.3216484901902</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28953,28 +29043,28 @@
         <v>0.1053</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1448546756269568</v>
+        <v>0.1432801780713491</v>
       </c>
       <c r="J3" t="n">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="K3" t="n">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01625519581980761</v>
+        <v>0.01600118656607241</v>
       </c>
       <c r="M3" t="n">
-        <v>6.94851329038003</v>
+        <v>6.934312570408936</v>
       </c>
       <c r="N3" t="n">
-        <v>70.89842515044221</v>
+        <v>70.71717049337363</v>
       </c>
       <c r="O3" t="n">
-        <v>8.420120257481019</v>
+        <v>8.409350182586859</v>
       </c>
       <c r="P3" t="n">
-        <v>349.0465610678963</v>
+        <v>349.0640467116945</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29031,28 +29121,28 @@
         <v>0.1495</v>
       </c>
       <c r="I4" t="n">
-        <v>0.009233014839166271</v>
+        <v>0.006688295286219798</v>
       </c>
       <c r="J4" t="n">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="K4" t="n">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="L4" t="n">
-        <v>7.527292269338126e-05</v>
+        <v>3.970754856619241e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>6.546152355289504</v>
+        <v>6.539305416397848</v>
       </c>
       <c r="N4" t="n">
-        <v>63.22617407747765</v>
+        <v>63.10311836805717</v>
       </c>
       <c r="O4" t="n">
-        <v>7.951488796286998</v>
+        <v>7.943747123874045</v>
       </c>
       <c r="P4" t="n">
-        <v>361.1565705735921</v>
+        <v>361.1848321188261</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29109,28 +29199,28 @@
         <v>0.1437</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.08167508019609913</v>
+        <v>-0.08213280763641233</v>
       </c>
       <c r="J5" t="n">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="K5" t="n">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007876835165738783</v>
+        <v>0.008013225150453995</v>
       </c>
       <c r="M5" t="n">
-        <v>5.593767428069027</v>
+        <v>5.580206788405981</v>
       </c>
       <c r="N5" t="n">
-        <v>46.91095544522312</v>
+        <v>46.77805275926574</v>
       </c>
       <c r="O5" t="n">
-        <v>6.849157279930365</v>
+        <v>6.839448278864731</v>
       </c>
       <c r="P5" t="n">
-        <v>368.0073167511848</v>
+        <v>368.0124000845192</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29187,28 +29277,28 @@
         <v>0.1645</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.01236430322361549</v>
+        <v>-0.01241544758431344</v>
       </c>
       <c r="J6" t="n">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="K6" t="n">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0001664468723451273</v>
+        <v>0.000168864586076567</v>
       </c>
       <c r="M6" t="n">
-        <v>5.743713572422441</v>
+        <v>5.727497275141995</v>
       </c>
       <c r="N6" t="n">
-        <v>51.27110401562619</v>
+        <v>51.12379716151272</v>
       </c>
       <c r="O6" t="n">
-        <v>7.160384348317218</v>
+        <v>7.150090710019889</v>
       </c>
       <c r="P6" t="n">
-        <v>361.5617677494131</v>
+        <v>361.5623358054604</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29265,28 +29355,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.07288814994514488</v>
+        <v>0.07431270490717386</v>
       </c>
       <c r="J7" t="n">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="K7" t="n">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005833204106648449</v>
+        <v>0.006097083185301</v>
       </c>
       <c r="M7" t="n">
-        <v>5.662227854386514</v>
+        <v>5.652638702939853</v>
       </c>
       <c r="N7" t="n">
-        <v>50.55303592057208</v>
+        <v>50.42643295143769</v>
       </c>
       <c r="O7" t="n">
-        <v>7.11006581689453</v>
+        <v>7.101157155804798</v>
       </c>
       <c r="P7" t="n">
-        <v>349.3099771111349</v>
+        <v>349.2941542788139</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29324,7 +29414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H695"/>
+  <dimension ref="A1:H697"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58517,6 +58607,90 @@
         </is>
       </c>
     </row>
+    <row r="696">
+      <c r="A696" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-07 21:59:48+00:00</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>-37.18106625659175,175.88506753042196</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>-37.18176247389245,175.8852982892533</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>-37.18246504203431,175.88548667382716</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>-37.18313420268326,175.8857906528888</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>-37.183813198534594,175.88606716656838</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>-37.1844980376365,175.88634623319427</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-23 21:59:53+00:00</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>-37.18106608687449,175.88506897833204</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>-37.18176219972936,175.88530062820533</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>-37.18246511562582,175.88548623304683</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>-37.18313405923056,175.88579118641707</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>-37.18381323404189,175.88606706311452</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>-37.184495603543496,175.8863528879267</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
